--- a/nomination_forms/033_biotech_firm_research_award_nomination_form--nomination_forms.xlsx
+++ b/nomination_forms/033_biotech_firm_research_award_nomination_form--nomination_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -528,11 +528,7 @@
           <t>Nominator Information</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Enter your details</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -555,11 +551,7 @@
           <t>First Name</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Your first name</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -582,11 +574,7 @@
           <t>Last Name</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Your last name</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -609,11 +597,7 @@
           <t>Professional Title</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Your job title</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -636,11 +620,7 @@
           <t>Organization</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Your company or institution</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -663,11 +643,7 @@
           <t>Email Address</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Contact email</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -690,11 +666,7 @@
           <t>Phone Number</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Contact number</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>yes</t>
@@ -704,27 +676,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nominee_information</t>
+          <t>award_category</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nominee Information</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Enter nominee details</t>
-        </is>
-      </c>
+          <t>Award Category</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -736,19 +704,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nominee_first_name</t>
+          <t>nomination_year</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>First Name</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Nominee's first name</t>
-        </is>
-      </c>
+          <t>Nomination Year</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>yes</t>
@@ -763,19 +727,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nominee_last_name</t>
+          <t>research_title</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Last Name</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Nominee's last name</t>
-        </is>
-      </c>
+          <t>Research Title</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>yes</t>
@@ -790,19 +750,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nominee_title</t>
+          <t>research_summary</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Professional Title</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Nominee's current position</t>
-        </is>
-      </c>
+          <t>Research Summary</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -812,24 +768,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nominee_organization</t>
+          <t>research_field</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Organization</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Nominee's company or institution</t>
-        </is>
-      </c>
+          <t>Research Field</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>yes</t>
@@ -839,27 +791,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nominee_department</t>
+          <t>research_duration</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Nominee's department or division</t>
-        </is>
-      </c>
+          <t>Research Duration</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -871,19 +819,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nominee_email</t>
+          <t>key_achievements</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Email Address</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Nominee's contact email</t>
-        </is>
-      </c>
+          <t>Key Achievements</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>yes</t>
@@ -893,51 +837,43 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>award_information</t>
+          <t>innovation_description</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Award Information</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Specify award details</t>
-        </is>
-      </c>
+          <t>Description of Innovation</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>award_category</t>
+          <t>impact_assessment</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Award Category</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Which award category</t>
-        </is>
-      </c>
+          <t>Impact Assessment</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>yes</t>
@@ -952,49 +888,41 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nomination_year</t>
+          <t>publications</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nomination Year</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Year for this nomination</t>
-        </is>
-      </c>
+          <t>Related Publications</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>research_details</t>
+          <t>cv_attached</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Research Details</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Describe the nominated work</t>
-        </is>
-      </c>
+          <t>CV or Resume Attached</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1006,19 +934,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>research_title</t>
+          <t>letters_of_support</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Research Title</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Title of the research or project</t>
-        </is>
-      </c>
+          <t>Number of Support Letters</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1033,49 +957,41 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>research_summary</t>
+          <t>additional_materials</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Research Summary</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Brief summary of the research</t>
-        </is>
-      </c>
+          <t>List any Other Supporting Materials</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>research_field</t>
+          <t>eligibility_confirmation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Research Field</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Primary field of research</t>
-        </is>
-      </c>
+          <t>Eligibility Confirmation</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1087,19 +1003,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>research_duration</t>
+          <t>eligibility_status</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Research Duration</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>How long was the research conducted</t>
-        </is>
-      </c>
+          <t>Eligibility Status</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1114,46 +1026,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>key_achievements</t>
+          <t>eligibility_exceptions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Key Achievements</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>List major accomplishments</t>
-        </is>
-      </c>
+          <t>Eligibility Exceptions</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>innovation_description</t>
+          <t>conflict_of_interest</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Description of Innovation</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>What makes this work innovative</t>
-        </is>
-      </c>
+          <t>Conflict of Interest</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1168,46 +1072,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>impact_assessment</t>
+          <t>conflict_description</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Impact Assessment</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Describe the impact of this work</t>
-        </is>
-      </c>
+          <t>Conflict Description</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>publications</t>
+          <t>previous_nominations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Related Publications</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>List key publications</t>
-        </is>
-      </c>
+          <t>Previous Nominations</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>no</t>
@@ -1222,46 +1118,42 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>patents</t>
+          <t>nomination_statement</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Patents</t>
+          <t>Nomination Statement</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>List any related patents</t>
+          <t>Why should this person or team receive this award</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>supporting_documents</t>
+          <t>submission_status</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Supporting Documents</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Documents to include</t>
-        </is>
-      </c>
+          <t>Submission Status</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>no</t>
@@ -1271,378 +1163,46 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>cv_attached</t>
+          <t>submission_date</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CV or Resume Attached</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Has nominee CV been included</t>
-        </is>
-      </c>
+          <t>Submission Date</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>letters_of_support</t>
+          <t>submission_notes</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Letters of Support</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Number of support letters</t>
-        </is>
-      </c>
+          <t>Submission Notes</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>additional_materials</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Additional Materials</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>List any other supporting materials</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
           <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>eligibility_confirmation</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Eligibility Confirmation</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Confirm nominee eligibility</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>eligibility_status</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Eligibility Status</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Is nominee eligible for this award</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>eligibility_exceptions</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Eligibility Exceptions</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Describe any exceptions if applicable</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>conflict_of_interest</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Conflict of Interest</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Do you have any conflict of interest</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>conflict_description</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Conflict Description</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Describe any conflicts</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>previous_nominations</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Previous Nominations</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Has nominee been nominated before</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>nomination_statement</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Nomination Statement</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Why should this person or team receive this award</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>reviewer_use_only</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>For Review Committee Use Only</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Scoring section</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>submission_status</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Submission Status</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Current status</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>submission_date</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Submission Date</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Date of nomination</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>nominator_signature</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Nominator Signature</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Confirm nomination accuracy</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1217,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2359,40 +1919,6 @@
       <c r="C41" t="inlineStr">
         <is>
           <t>Not Selected</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>nominator_signature_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>i_certify_this_nomination_is_accurate</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>I certify this nomination is accurate</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>nominator_signature_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>i_endorse_this_nomination</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>I endorse this nomination</t>
         </is>
       </c>
     </row>
